--- a/templates/sensibilizacion.xlsx
+++ b/templates/sensibilizacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaron\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaron\Desktop\RECA_INCLUSION_LABORAL\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E9517E-F192-4CDC-8B6E-F6E8307B90E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF379AA8-476D-42F8-81D3-A9F0C3F3C0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -547,67 +547,38 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -615,28 +586,43 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -646,6 +632,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -952,27 +944,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="e" vm="1">
+      <c r="A1" s="16" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="24" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="22"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="18"/>
       <c r="R1" s="4" t="s">
         <v>0</v>
       </c>
@@ -981,23 +973,23 @@
       </c>
     </row>
     <row r="2" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="17"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="21"/>
       <c r="R2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1006,23 +998,23 @@
       </c>
     </row>
     <row r="3" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="25"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="17"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="21"/>
       <c r="R3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1031,50 +1023,50 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="26"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="43" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="S4" s="13"/>
+      <c r="S4" s="12"/>
     </row>
     <row r="5" spans="1:26" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="12"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1084,202 +1076,202 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="13"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="12"/>
     </row>
     <row r="7" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="23" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="49"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="12"/>
     </row>
     <row r="8" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="23" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="13"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="12"/>
     </row>
     <row r="9" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="23" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="13"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="12"/>
     </row>
     <row r="10" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="23" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="13"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="12"/>
     </row>
     <row r="11" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="32" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="13"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="12"/>
     </row>
     <row r="12" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="36" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="13"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="12"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="12"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -1289,142 +1281,142 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="44">
+      <c r="A14" s="37">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="12"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="30"/>
-      <c r="B15" s="20" t="s">
+      <c r="A15" s="38"/>
+      <c r="B15" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="17"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="21"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="38"/>
+      <c r="B16" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="17"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="21"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="30"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="17"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="21"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="30"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="38"/>
+      <c r="B18" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="17"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="21"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="17"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="21"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -1434,399 +1426,399 @@
       <c r="Z19" s="7"/>
     </row>
     <row r="20" spans="1:26" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29">
+      <c r="A20" s="40">
         <v>2</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="22"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="18"/>
     </row>
     <row r="21" spans="1:26" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="16"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="24"/>
     </row>
     <row r="22" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="37">
+      <c r="A22" s="41">
         <v>3</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="22"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="18"/>
     </row>
     <row r="23" spans="1:26" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25"/>
-      <c r="B23" s="46" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="17"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="21"/>
     </row>
     <row r="24" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="26"/>
-      <c r="B24" s="52" t="s">
+      <c r="A24" s="22"/>
+      <c r="B24" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="54"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="47"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="47"/>
+      <c r="S24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="12"/>
     </row>
     <row r="26" spans="1:26" ht="137.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="27"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="16"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="24"/>
     </row>
     <row r="27" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="12"/>
     </row>
     <row r="28" spans="1:26" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="33"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="13"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="12"/>
     </row>
     <row r="29" spans="1:26" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="33"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="13"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="12"/>
     </row>
     <row r="30" spans="1:26" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="33" t="s">
+      <c r="A30" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="13"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="12"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="13"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="12"/>
     </row>
     <row r="32" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="49"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="12"/>
       <c r="J32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="K32" s="34"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="13"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="12"/>
     </row>
     <row r="33" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="13"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="12"/>
       <c r="J33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K33" s="32"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="13"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="12"/>
     </row>
     <row r="34" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="13"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="12"/>
       <c r="J34" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K34" s="32"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="13"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="12"/>
     </row>
     <row r="35" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="13"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="12"/>
       <c r="J35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K35" s="32"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="13"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="12"/>
     </row>
     <row r="36" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="12"/>
-      <c r="P36" s="12"/>
-      <c r="Q36" s="12"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="12"/>
     </row>
     <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
@@ -1893,11 +1885,11 @@
     </row>
     <row r="40" spans="1:19" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
@@ -6796,49 +6788,13 @@
     <row r="1002" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="A1:E4"/>
-    <mergeCell ref="F1:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="A5:S5"/>
-    <mergeCell ref="A6:S6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="K35:S35"/>
-    <mergeCell ref="A36:S36"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="K29:S29"/>
-    <mergeCell ref="A30:S30"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="K34:S34"/>
-    <mergeCell ref="A31:S31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="K32:S32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="K33:S33"/>
+    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="B13:S13"/>
+    <mergeCell ref="B14:S14"/>
     <mergeCell ref="B19:S19"/>
     <mergeCell ref="A26:S26"/>
     <mergeCell ref="A27:S27"/>
@@ -6855,13 +6811,49 @@
     <mergeCell ref="B24:S24"/>
     <mergeCell ref="A25:S25"/>
     <mergeCell ref="B17:S17"/>
-    <mergeCell ref="B18:S18"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="B13:S13"/>
-    <mergeCell ref="B14:S14"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="K29:S29"/>
+    <mergeCell ref="A30:S30"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="K34:S34"/>
+    <mergeCell ref="A31:S31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="K32:S32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="K33:S33"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="K35:S35"/>
+    <mergeCell ref="A36:S36"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="A1:E4"/>
+    <mergeCell ref="F1:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="A5:S5"/>
+    <mergeCell ref="A6:S6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="D9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:K11"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K32" xr:uid="{00000000-0002-0000-0B00-000000000000}">

--- a/templates/sensibilizacion.xlsx
+++ b/templates/sensibilizacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaron\Desktop\RECA_INCLUSION_LABORAL\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF379AA8-476D-42F8-81D3-A9F0C3F3C0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88EFA05-A8AE-4268-BE15-6DD3F47DC1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,28 +34,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,59 +525,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -612,12 +566,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -633,11 +588,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -656,68 +634,53 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>154877</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67FFF12E-3E05-0001-15AB-794A00592E34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="1"/>
+          <a:ext cx="2895599" cy="640651"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -944,27 +907,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="16" t="s">
+      <c r="A1" s="47"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="18"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="34"/>
       <c r="R1" s="4" t="s">
         <v>0</v>
       </c>
@@ -973,23 +934,23 @@
       </c>
     </row>
     <row r="2" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="21"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13"/>
       <c r="R2" s="4" t="s">
         <v>1</v>
       </c>
@@ -998,23 +959,23 @@
       </c>
     </row>
     <row r="3" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="21"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="13"/>
       <c r="R3" s="4" t="s">
         <v>19</v>
       </c>
@@ -1023,50 +984,50 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="25" t="s">
+      <c r="A4" s="31"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="S4" s="12"/>
+      <c r="S4" s="16"/>
     </row>
     <row r="5" spans="1:26" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="12"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="16"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1076,202 +1037,202 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="12"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="16"/>
     </row>
     <row r="7" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="13" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="12"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="16"/>
     </row>
     <row r="8" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="13" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="12"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="16"/>
     </row>
     <row r="9" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="13" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="12"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="16"/>
     </row>
     <row r="10" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="13" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="12"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="16"/>
     </row>
     <row r="11" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="11" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="12"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="16"/>
     </row>
     <row r="12" spans="1:26" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="49" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="32"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="12"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="16"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="12"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="16"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -1281,142 +1242,142 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="37">
+      <c r="A14" s="25">
         <v>1</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="12"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="16"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="38"/>
-      <c r="B15" s="42" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="21"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="13"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="38"/>
-      <c r="B16" s="42" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="21"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="13"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="42" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="21"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="13"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="38"/>
-      <c r="B18" s="42" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="21"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="13"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="39"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="21"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="13"/>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
@@ -1426,399 +1387,399 @@
       <c r="Z19" s="7"/>
     </row>
     <row r="20" spans="1:26" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="40">
+      <c r="A20" s="28">
         <v>2</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="18"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="39"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="24"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="23"/>
     </row>
     <row r="22" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="41">
+      <c r="A22" s="29">
         <v>3</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="18"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19"/>
-      <c r="B23" s="45" t="s">
+      <c r="A23" s="30"/>
+      <c r="B23" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="21"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="13"/>
     </row>
     <row r="24" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="46" t="s">
+      <c r="A24" s="31"/>
+      <c r="B24" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47"/>
-      <c r="S24" s="48"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="39"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="12"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+      <c r="S25" s="16"/>
     </row>
     <row r="26" spans="1:26" ht="137.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="36"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="24"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="23"/>
     </row>
     <row r="27" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="12"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="16"/>
     </row>
     <row r="28" spans="1:26" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="32"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="12"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="16"/>
     </row>
     <row r="29" spans="1:26" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="32"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="12"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="16"/>
     </row>
     <row r="30" spans="1:26" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="12"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="16"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
+      <c r="A31" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="12"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="16"/>
     </row>
     <row r="32" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="12"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="16"/>
       <c r="J32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K32" s="34"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="12"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="16"/>
     </row>
     <row r="33" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="12"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="16"/>
       <c r="J33" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="12"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="16"/>
     </row>
     <row r="34" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="12"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="16"/>
       <c r="J34" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="12"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="16"/>
     </row>
     <row r="35" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="12"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="16"/>
       <c r="J35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="14"/>
-      <c r="S35" s="12"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="16"/>
     </row>
     <row r="36" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="12"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="16"/>
     </row>
     <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
@@ -1885,11 +1846,11 @@
     </row>
     <row r="40" spans="1:19" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
@@ -6788,13 +6749,49 @@
     <row r="1002" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="B18:S18"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="B13:S13"/>
-    <mergeCell ref="B14:S14"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:S10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="D9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:S9"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="A1:E4"/>
+    <mergeCell ref="F1:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="A5:S5"/>
+    <mergeCell ref="A6:S6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="K35:S35"/>
+    <mergeCell ref="A36:S36"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="K29:S29"/>
+    <mergeCell ref="A30:S30"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="K34:S34"/>
+    <mergeCell ref="A31:S31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="K32:S32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="K33:S33"/>
     <mergeCell ref="B19:S19"/>
     <mergeCell ref="A26:S26"/>
     <mergeCell ref="A27:S27"/>
@@ -6811,49 +6808,13 @@
     <mergeCell ref="B24:S24"/>
     <mergeCell ref="A25:S25"/>
     <mergeCell ref="B17:S17"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="K29:S29"/>
-    <mergeCell ref="A30:S30"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="K34:S34"/>
-    <mergeCell ref="A31:S31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="K32:S32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="K33:S33"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="K35:S35"/>
-    <mergeCell ref="A36:S36"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="A1:E4"/>
-    <mergeCell ref="F1:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="A5:S5"/>
-    <mergeCell ref="A6:S6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:S9"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:S11"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:S10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="B13:S13"/>
+    <mergeCell ref="B14:S14"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K32" xr:uid="{00000000-0002-0000-0B00-000000000000}">
@@ -6875,5 +6836,6 @@
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>